--- a/static/samples/teachers_upload_sample.xlsx
+++ b/static/samples/teachers_upload_sample.xlsx
@@ -26,16 +26,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00888888"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,7 +57,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,39 +427,48 @@
   </sheetPr>
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>first_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>last_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>subjects</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>streams</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>class_teacher</t>
         </is>
@@ -481,7 +497,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MATH,PHY</t>
+          <t>MAT,PHY</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -569,22 +585,79 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ann</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Waweru</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ann.waweru@school.ac.ke</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0744444444</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>KISW,FAS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t># NOTE:</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n"/>
-      <c r="C6" s="1" t="n"/>
-      <c r="D6" s="1" t="n"/>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>Comma-separated subject CODES matching catalog-activated subjects. Unknown codes are skipped with a warning.</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="n"/>
-      <c r="G6" s="1" t="n"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ochieng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>james.ochieng@school.ac.ke</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0755555555</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HIST,GEO,BST</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2A,2B</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
